--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/spec-tech/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
